--- a/data/trans_dic/P19F$noche-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57,64; 71,84</t>
+          <t>58,17; 72,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,91; 79,54</t>
+          <t>66,06; 80,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,93; 74,07</t>
+          <t>63,77; 74,22</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,68; 60,93</t>
+          <t>48,29; 60,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,62; 71,81</t>
+          <t>58,55; 71,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,09; 63,95</t>
+          <t>55,01; 64,26</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,31; 85,24</t>
+          <t>71,42; 84,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,37; 93,84</t>
+          <t>80,2; 92,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,88; 86,62</t>
+          <t>77,43; 87,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,6; 83,1</t>
+          <t>71,2; 83,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,12; 86,48</t>
+          <t>74,37; 85,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,97; 82,78</t>
+          <t>75,15; 83,14</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,07; 97,04</t>
+          <t>89,48; 97,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,59; 97,55</t>
+          <t>90,38; 97,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,15; 96,62</t>
+          <t>91,35; 96,7</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,4; 84,74</t>
+          <t>71,16; 84,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,45; 85,65</t>
+          <t>73,4; 85,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,23; 83,62</t>
+          <t>75,29; 84,01</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,08; 81,25</t>
+          <t>72,6; 81,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,07; 82,17</t>
+          <t>73,1; 82,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,45; 80,7</t>
+          <t>74,35; 80,45</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>92,24; 96,95</t>
+          <t>91,91; 96,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85,72; 92,98</t>
+          <t>86,36; 93,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,21</t>
+          <t>90,25; 94,28</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>75,56; 79,59</t>
+          <t>75,69; 79,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78,87; 82,56</t>
+          <t>78,57; 82,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77,76; 80,66</t>
+          <t>77,73; 80,68</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>103312; 128782</t>
+          <t>104270; 130275</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>105081; 128752</t>
+          <t>106930; 129892</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>218075; 252668</t>
+          <t>217530; 253176</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>120772; 154349</t>
+          <t>122323; 153270</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138872; 170112</t>
+          <t>138707; 169166</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>270052; 313496</t>
+          <t>269679; 314998</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99554; 117366</t>
+          <t>98328; 116981</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78467; 91622</t>
+          <t>78299; 90680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180908; 203833</t>
+          <t>182211; 204734</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>149612; 173646</t>
+          <t>148775; 173510</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>169962; 195664</t>
+          <t>168250; 192909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>326264; 360237</t>
+          <t>327033; 361817</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>129579; 141182</t>
+          <t>130176; 141688</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>133962; 144251</t>
+          <t>133655; 144313</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267388; 283460</t>
+          <t>267992; 283673</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>105035; 124670</t>
+          <t>104694; 124546</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130701; 152420</t>
+          <t>130611; 151801</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>244532; 271814</t>
+          <t>244727; 273096</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>274727; 309699</t>
+          <t>276697; 312353</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>263251; 296017</t>
+          <t>263337; 296071</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>551995; 598283</t>
+          <t>551238; 596444</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>300554; 315918</t>
+          <t>299500; 315556</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>286140; 310372</t>
+          <t>288277; 310789</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>594281; 621441</t>
+          <t>595327; 621908</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1344079; 1415670</t>
+          <t>1346408; 1417911</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1374368; 1438597</t>
+          <t>1369135; 1436644</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2738106; 2840362</t>
+          <t>2737006; 2840885</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$noche-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,17; 72,68</t>
+          <t>58,0; 72,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,06; 80,24</t>
+          <t>65,61; 79,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,77; 74,22</t>
+          <t>63,56; 74,28</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,29; 60,51</t>
+          <t>48,01; 60,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,55; 71,41</t>
+          <t>58,64; 71,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,01; 64,26</t>
+          <t>55,17; 64,03</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,42; 84,96</t>
+          <t>71,93; 85,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,2; 92,88</t>
+          <t>79,86; 93,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,43; 87,0</t>
+          <t>77,6; 86,95</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,2; 83,04</t>
+          <t>71,25; 82,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,37; 85,27</t>
+          <t>75,19; 86,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,15; 83,14</t>
+          <t>75,13; 83,36</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,48; 97,39</t>
+          <t>89,5; 97,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,38; 97,59</t>
+          <t>89,17; 97,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,35; 96,7</t>
+          <t>91,46; 96,68</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,16; 84,66</t>
+          <t>72,01; 84,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,4; 85,3</t>
+          <t>73,65; 85,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,29; 84,01</t>
+          <t>75,01; 83,64</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,6; 81,95</t>
+          <t>72,4; 81,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,1; 82,18</t>
+          <t>73,34; 82,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,35; 80,45</t>
+          <t>73,77; 80,48</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,91; 96,84</t>
+          <t>91,73; 96,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,36; 93,1</t>
+          <t>85,88; 93,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,25; 94,28</t>
+          <t>89,84; 94,2</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>75,69; 79,71</t>
+          <t>75,62; 79,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78,57; 82,45</t>
+          <t>78,66; 82,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77,73; 80,68</t>
+          <t>77,77; 80,66</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104270; 130275</t>
+          <t>103961; 130656</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106930; 129892</t>
+          <t>106209; 129235</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>217530; 253176</t>
+          <t>216832; 253405</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122323; 153270</t>
+          <t>121620; 153448</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138707; 169166</t>
+          <t>138911; 168647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>269679; 314998</t>
+          <t>270459; 313885</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98328; 116981</t>
+          <t>99039; 117153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78299; 90680</t>
+          <t>77971; 91087</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182211; 204734</t>
+          <t>182605; 204598</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148775; 173510</t>
+          <t>148880; 173312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168250; 192909</t>
+          <t>170112; 195084</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>327033; 361817</t>
+          <t>326964; 362758</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>130176; 141688</t>
+          <t>130212; 141596</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>133655; 144313</t>
+          <t>131865; 144145</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267992; 283673</t>
+          <t>268296; 283627</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>104694; 124546</t>
+          <t>105940; 124955</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130611; 151801</t>
+          <t>131059; 153020</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>244727; 273096</t>
+          <t>243832; 271870</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>276697; 312353</t>
+          <t>275950; 310510</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>263337; 296071</t>
+          <t>264209; 295996</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>551238; 596444</t>
+          <t>546954; 596661</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>299500; 315556</t>
+          <t>298919; 315532</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>288277; 310789</t>
+          <t>286689; 310683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>595327; 621908</t>
+          <t>592652; 621370</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1346408; 1417911</t>
+          <t>1345093; 1415764</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1369135; 1436644</t>
+          <t>1370750; 1440189</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2737006; 2840885</t>
+          <t>2738440; 2840308</t>
         </is>
       </c>
     </row>
